--- a/backend/super_safe_file.xlsx
+++ b/backend/super_safe_file.xlsx
@@ -448,7 +448,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col width="16.04" customWidth="1" style="2" min="1" max="1"/>
   </cols>
@@ -478,12 +478,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>wiktoriatec</t>
+          <t>wiktoriatecza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bMGKigY</t>
+          <t>wj-k-wg</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>artursad</t>
+          <t>artursadurski</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M2aM6Ag</t>
+          <t>S7ZowZQ</t>
         </is>
       </c>
     </row>
@@ -512,12 +512,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>marcinkos</t>
+          <t>marcinkostrzewa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4yb155s</t>
+          <t>w_zn5fE</t>
         </is>
       </c>
     </row>
@@ -529,12 +529,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>marcinmis</t>
+          <t>marcinmiskiewicz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>qM2-BSI</t>
+          <t>XFin4Bs</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>kacperbor</t>
+          <t>kacperborys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SWxef04</t>
+          <t>N0pL00g</t>
         </is>
       </c>
     </row>

--- a/backend/super_safe_file.xlsx
+++ b/backend/super_safe_file.xlsx
@@ -476,14 +476,14 @@
           <t>Wiktoria Tecza</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>wiktoriatecza</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>wj-k-wg</t>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Eb61mps</t>
         </is>
       </c>
     </row>
@@ -493,14 +493,14 @@
           <t>Artur Sadurski</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>artursadurski</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S7ZowZQ</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BVON7T0</t>
         </is>
       </c>
     </row>
@@ -510,14 +510,14 @@
           <t>Marcin Kostrzewa</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>marcinkostrzewa</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>w_zn5fE</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>YvXENJw</t>
         </is>
       </c>
     </row>
@@ -527,14 +527,14 @@
           <t>Marcin Miskiewicz</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>marcinmiskiewicz</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>XFin4Bs</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>xCoq5Qo</t>
         </is>
       </c>
     </row>
@@ -544,14 +544,14 @@
           <t>Kacper Borys</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>kacperborys</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>N0pL00g</t>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Sgq1_kU</t>
         </is>
       </c>
     </row>

--- a/backend/super_safe_file.xlsx
+++ b/backend/super_safe_file.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Eb61mps</t>
+          <t>3PIu7f0</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>BVON7T0</t>
+          <t>Ls6Hdio</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>YvXENJw</t>
+          <t>mCkwEzc</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>xCoq5Qo</t>
+          <t>uWoFKuk</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sgq1_kU</t>
+          <t>K4Yiegc</t>
         </is>
       </c>
     </row>

--- a/backend/super_safe_file.xlsx
+++ b/backend/super_safe_file.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3PIu7f0</t>
+          <t>jGSI56M</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Ls6Hdio</t>
+          <t>R_iygpA</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>mCkwEzc</t>
+          <t>FTY2308</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>uWoFKuk</t>
+          <t>LVOrxhY</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>K4Yiegc</t>
+          <t>12HH0pY</t>
         </is>
       </c>
     </row>

--- a/backend/super_safe_file.xlsx
+++ b/backend/super_safe_file.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>jGSI56M</t>
+          <t>TXv47aI</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>R_iygpA</t>
+          <t>A7Z1h9c</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>FTY2308</t>
+          <t>SzlNWWA</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>LVOrxhY</t>
+          <t>XiFBVC4</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12HH0pY</t>
+          <t>CnuE2XA</t>
         </is>
       </c>
     </row>
